--- a/data/eyes.xlsx
+++ b/data/eyes.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\basic_stats_R\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\bookdown-crc-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D329B6-DC96-457D-8E5B-6E6837BD677F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D0DF01-D07B-4CE3-AD7D-E58151EB09C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF14AE2F-681D-4C22-8C90-F7521819558B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -36,7 +52,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -44,7 +60,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -69,17 +85,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -102,44 +119,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -186,12 +203,12 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -247,179 +264,179 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E55556D-F087-4E89-8C01-91D79525FD3B}">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -428,63 +445,199 @@
         <v>488</v>
       </c>
       <c r="B2">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="B3">
-        <v>478</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B4">
-        <v>492</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B5">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="B6">
-        <v>436</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="B7">
-        <v>398</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="B8">
-        <v>464</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>425</v>
+      </c>
+      <c r="B9">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>492</v>
+      </c>
+      <c r="B10">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>478</v>
+      </c>
+      <c r="B11">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>422</v>
+      </c>
+      <c r="B12">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>486</v>
+      </c>
+      <c r="B13">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>485</v>
+      </c>
+      <c r="B14">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>479</v>
+      </c>
+      <c r="B15">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>422</v>
+      </c>
+      <c r="B16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>454</v>
+      </c>
+      <c r="B17">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>479</v>
+      </c>
+      <c r="B18">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>432</v>
+      </c>
+      <c r="B19">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>491</v>
+      </c>
+      <c r="B20">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>454</v>
+      </c>
+      <c r="B21">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>413</v>
+      </c>
+      <c r="B22">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>489</v>
+      </c>
+      <c r="B23">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>438</v>
+      </c>
+      <c r="B24">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>488</v>
+      </c>
+      <c r="B25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>455</v>
+      </c>
+      <c r="B26">
         <v>460</v>
-      </c>
-      <c r="B9">
-        <v>476</v>
       </c>
     </row>
   </sheetData>
